--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -565,67 +565,67 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1976</v>
+        <v>16.1139</v>
       </c>
       <c r="E2" t="n">
-        <v>19.0944</v>
+        <v>18.099</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8965</v>
+        <v>-1.985099999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>14.274</v>
+        <v>14.1642</v>
       </c>
       <c r="H2" t="n">
-        <v>19.7397</v>
+        <v>19.6155</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.4657</v>
+        <v>-5.4519</v>
       </c>
       <c r="J2" t="n">
-        <v>15.8028</v>
+        <v>15.3552</v>
       </c>
       <c r="K2" t="n">
-        <v>11.2293</v>
+        <v>10.9191</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5738</v>
+        <v>4.4364</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5288</v>
+        <v>-1.191299999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.5107</v>
+        <v>8.6967</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.0395</v>
+        <v>-9.887699999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.153799999999999</v>
+        <v>-4.197</v>
       </c>
       <c r="Q2" t="n">
-        <v>-14.5374</v>
+        <v>-14.6898</v>
       </c>
       <c r="R2" t="n">
-        <v>10.3839</v>
+        <v>10.4925</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3109</v>
+        <v>2.3415</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2895</v>
+        <v>3.0243</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.978</v>
+        <v>-0.6828000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>3.7659</v>
+        <v>3.8052</v>
       </c>
       <c r="W2" t="n">
-        <v>14.5392</v>
+        <v>14.409</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.7736</v>
+        <v>-10.6035</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>15.4458</v>
+        <v>15.378</v>
       </c>
       <c r="E3" t="n">
-        <v>10.0254</v>
+        <v>9.0093</v>
       </c>
       <c r="F3" t="n">
-        <v>5.421</v>
+        <v>6.3687</v>
       </c>
       <c r="G3" t="n">
-        <v>16.2063</v>
+        <v>16.0614</v>
       </c>
       <c r="H3" t="n">
-        <v>16.6245</v>
+        <v>16.4619</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4181999999999999</v>
+        <v>-0.4005000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>13.1466</v>
+        <v>12.6105</v>
       </c>
       <c r="K3" t="n">
-        <v>12.6948</v>
+        <v>12.2514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4512000000000003</v>
+        <v>0.3588000000000002</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0603</v>
+        <v>3.4509</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9291</v>
+        <v>4.210500000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8694000000000002</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>4.153799999999999</v>
+        <v>4.197</v>
       </c>
       <c r="Q3" t="n">
-        <v>-8.9994</v>
+        <v>-9.0936</v>
       </c>
       <c r="R3" t="n">
-        <v>13.1532</v>
+        <v>13.2903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6705000000000001</v>
+        <v>0.6999000000000002</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5624</v>
+        <v>4.257</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.8919</v>
+        <v>-3.5568</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.5848</v>
+        <v>-5.5803</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3158</v>
+        <v>1.2357</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.9006</v>
+        <v>-6.816000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8.523899999999999</v>
+        <v>8.551500000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4691</v>
+        <v>0.4623</v>
       </c>
       <c r="F4" t="n">
-        <v>7.0551</v>
+        <v>8.0892</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.7964</v>
+        <v>-13.8111</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.7034</v>
+        <v>-7.7583</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.0924</v>
+        <v>-6.0528</v>
       </c>
       <c r="J4" t="n">
-        <v>-12.8292</v>
+        <v>-13.2795</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.6399</v>
+        <v>-12.9834</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1892999999999998</v>
+        <v>-0.2961000000000009</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9672000000000001</v>
+        <v>-0.5316000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9359</v>
+        <v>5.225099999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.9034</v>
+        <v>-5.7567</v>
       </c>
       <c r="P4" t="n">
-        <v>6.9225</v>
+        <v>6.9951</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.3073</v>
+        <v>-8.394</v>
       </c>
       <c r="R4" t="n">
-        <v>15.2298</v>
+        <v>15.3891</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5589000000000001</v>
+        <v>0.5931000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>6.0117</v>
+        <v>5.7141</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.4528</v>
+        <v>-5.1207</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8389</v>
+        <v>14.7747</v>
       </c>
       <c r="W4" t="n">
-        <v>16.5936</v>
+        <v>16.4217</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7544</v>
+        <v>-1.6476</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9725</v>
+        <v>2.0691</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7826</v>
+        <v>-2.6976</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7548</v>
+        <v>4.767</v>
       </c>
       <c r="G5" t="n">
-        <v>1.820700000000001</v>
+        <v>1.934100000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.276</v>
+        <v>-3.1617</v>
       </c>
       <c r="I5" t="n">
-        <v>5.097</v>
+        <v>5.0961</v>
       </c>
       <c r="J5" t="n">
-        <v>6.0507</v>
+        <v>5.693700000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.1309</v>
+        <v>-2.3628</v>
       </c>
       <c r="L5" t="n">
-        <v>8.1816</v>
+        <v>8.0562</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.2297</v>
+        <v>-3.7593</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1448</v>
+        <v>-0.7991999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.0846</v>
+        <v>-2.9604</v>
       </c>
       <c r="P5" t="n">
-        <v>-6.2301</v>
+        <v>-6.2955</v>
       </c>
       <c r="Q5" t="n">
-        <v>-16.6143</v>
+        <v>-16.7883</v>
       </c>
       <c r="R5" t="n">
-        <v>10.3839</v>
+        <v>10.4925</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7078</v>
+        <v>5.781</v>
       </c>
       <c r="T5" t="n">
-        <v>7.4652</v>
+        <v>7.1613</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.7574</v>
+        <v>-1.3803</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6741</v>
+        <v>0.6497999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3158</v>
+        <v>1.2357</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.642</v>
+        <v>-0.5859</v>
       </c>
     </row>
     <row r="6">
@@ -877,19 +877,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5075999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4356</v>
+        <v>-3.3096</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4776000000000001</v>
+        <v>-0.5982</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9583</v>
+        <v>-2.7117</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.477</v>
+        <v>-3.3759</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.0197</v>
+        <v>-3.9402</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5427</v>
+        <v>0.5643</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1256</v>
+        <v>-1.1442</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.458</v>
+        <v>-1.4742</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3321</v>
+        <v>0.3303</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.352</v>
+        <v>-2.2317</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.5623</v>
+        <v>-2.4657</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2103</v>
+        <v>0.2343</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0769</v>
+        <v>2.0985</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0769</v>
+        <v>2.0985</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7569</v>
+        <v>0.7578</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2097</v>
+        <v>0.1341</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5478</v>
+        <v>0.6234</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7924</v>
+        <v>-2.79</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4386</v>
+        <v>0.4119</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.4294</v>
+        <v>-5.262</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.1703</v>
+        <v>-4.494899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2585</v>
+        <v>-0.7668000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4528</v>
+        <v>2.6025</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7607999999999998</v>
+        <v>-0.6224999999999997</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2136</v>
+        <v>3.2253</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0193</v>
+        <v>1.9107</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8578</v>
+        <v>2.7801</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8385</v>
+        <v>-0.8691</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4335</v>
+        <v>0.6917999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.6189</v>
+        <v>-3.4026</v>
       </c>
       <c r="O8" t="n">
-        <v>4.0521</v>
+        <v>4.0938</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6924</v>
+        <v>0.6996</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1535</v>
+        <v>-4.197</v>
       </c>
       <c r="R8" t="n">
-        <v>4.846200000000001</v>
+        <v>4.8966</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.3436</v>
+        <v>-5.3619</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.0364</v>
+        <v>-2.2089</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.3069</v>
+        <v>-3.1533</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.0823</v>
+        <v>-8.1006</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.8722</v>
+        <v>-11.9838</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7899</v>
+        <v>3.8835</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9805</v>
+        <v>-2.9616</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8631</v>
+        <v>-0.8508</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1174</v>
+        <v>-2.1108</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.8957</v>
+        <v>-4.9008</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3718</v>
+        <v>-2.3754</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.5239</v>
+        <v>-2.5254</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9152</v>
+        <v>1.9392</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5084</v>
+        <v>1.5243</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4065</v>
+        <v>0.4149</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.538</v>
+        <v>-5.5959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.9225</v>
+        <v>-6.995100000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3845</v>
+        <v>1.3989</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4362</v>
+        <v>0.4569</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.05399999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4902</v>
+        <v>0.5451</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.454599999999999</v>
+        <v>-8.434200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5649</v>
+        <v>-6.947699999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.89</v>
+        <v>-1.4865</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6842</v>
+        <v>-1.5855</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.36</v>
+        <v>-3.2895</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6758</v>
+        <v>1.7043</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7367999999999997</v>
+        <v>-0.7971000000000004</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2909</v>
+        <v>-1.3473</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5538</v>
+        <v>0.5502</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9473999999999999</v>
+        <v>-0.7884</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0694</v>
+        <v>-1.9422</v>
       </c>
       <c r="O10" t="n">
-        <v>1.122</v>
+        <v>1.1541</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.307</v>
+        <v>-8.394</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.076</v>
+        <v>-11.1921</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7693</v>
+        <v>2.7981</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2749</v>
+        <v>2.3226</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4754999999999999</v>
+        <v>-0.5853</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7504</v>
+        <v>2.9079</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7382999999999997</v>
+        <v>-0.7773000000000003</v>
       </c>
       <c r="W10" t="n">
-        <v>5.7237</v>
+        <v>5.6268</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.462</v>
+        <v>-6.4041</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.545100000000001</v>
+        <v>-9.6591</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.359499999999999</v>
+        <v>-9.110100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1856</v>
+        <v>-0.5489999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.7196</v>
+        <v>-7.644</v>
       </c>
       <c r="H11" t="n">
-        <v>14.9046</v>
+        <v>14.8794</v>
       </c>
       <c r="I11" t="n">
-        <v>-22.6245</v>
+        <v>-22.5234</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4441</v>
+        <v>-2.6874</v>
       </c>
       <c r="K11" t="n">
-        <v>9.930299999999999</v>
+        <v>9.713700000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.3747</v>
+        <v>-12.4011</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.2755</v>
+        <v>-4.9566</v>
       </c>
       <c r="N11" t="n">
-        <v>4.974299999999999</v>
+        <v>5.165699999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-10.2501</v>
+        <v>-10.122</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0769</v>
+        <v>-2.0985</v>
       </c>
       <c r="Q11" t="n">
-        <v>-14.5374</v>
+        <v>-14.6898</v>
       </c>
       <c r="R11" t="n">
-        <v>12.4608</v>
+        <v>12.5907</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.7078</v>
+        <v>-5.7807</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4603</v>
+        <v>2.2287</v>
       </c>
       <c r="U11" t="n">
-        <v>-8.167199999999999</v>
+        <v>-8.0097</v>
       </c>
       <c r="V11" t="n">
-        <v>5.9592</v>
+        <v>5.864699999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>6.1623</v>
+        <v>6.0387</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2034</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.1136</v>
+        <v>-19.4547</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.4471</v>
+        <v>-18.7809</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6665</v>
+        <v>-0.6735000000000004</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2395</v>
+        <v>11.2227</v>
       </c>
       <c r="H12" t="n">
-        <v>10.293</v>
+        <v>10.3113</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9465000000000001</v>
+        <v>0.9116999999999997</v>
       </c>
       <c r="J12" t="n">
-        <v>16.1793</v>
+        <v>15.6543</v>
       </c>
       <c r="K12" t="n">
-        <v>8.9229</v>
+        <v>8.571000000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>7.2564</v>
+        <v>7.082999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.9398</v>
+        <v>-4.4316</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3701</v>
+        <v>1.7403</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.3099</v>
+        <v>-6.171600000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-29.0751</v>
+        <v>-29.3793</v>
       </c>
       <c r="Q12" t="n">
-        <v>-40.8435</v>
+        <v>-41.2707</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7684</v>
+        <v>11.8914</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3907</v>
+        <v>-2.3595</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1092</v>
+        <v>2.8098</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.4999</v>
+        <v>-5.1693</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1127</v>
+        <v>1.061699999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>4.1082</v>
+        <v>4.0257</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9955</v>
+        <v>-2.964</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.8142</v>
+        <v>-30.7851</v>
       </c>
       <c r="E13" t="n">
-        <v>-27.8391</v>
+        <v>-28.8648</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.975399999999999</v>
+        <v>-1.9206</v>
       </c>
       <c r="G13" t="n">
-        <v>-36.4995</v>
+        <v>-36.4023</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.2703</v>
+        <v>-3.171</v>
       </c>
       <c r="I13" t="n">
-        <v>-33.2292</v>
+        <v>-33.231</v>
       </c>
       <c r="J13" t="n">
-        <v>-29.5989</v>
+        <v>-29.9349</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.732299999999999</v>
+        <v>-9.8931</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.8666</v>
+        <v>-20.0418</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.900600000000001</v>
+        <v>-6.4674</v>
       </c>
       <c r="N13" t="n">
-        <v>6.4623</v>
+        <v>6.7218</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.3629</v>
+        <v>-13.1895</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4614</v>
+        <v>-3.4974</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.3836</v>
+        <v>-19.5861</v>
       </c>
       <c r="R13" t="n">
-        <v>15.9222</v>
+        <v>16.0887</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8881</v>
+        <v>2.8848</v>
       </c>
       <c r="T13" t="n">
-        <v>7.3422</v>
+        <v>7.024800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.4544</v>
+        <v>-4.1403</v>
       </c>
       <c r="V13" t="n">
-        <v>6.258599999999999</v>
+        <v>6.2301</v>
       </c>
       <c r="W13" t="n">
-        <v>13.8012</v>
+        <v>13.6314</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.5423</v>
+        <v>-7.4016</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-43.2426</v>
+        <v>-43.39320000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-47.9244</v>
+        <v>-55.9074</v>
       </c>
       <c r="F14" t="n">
-        <v>4.682400000000001</v>
+        <v>12.5148</v>
       </c>
       <c r="G14" t="n">
-        <v>-20.67149999999999</v>
+        <v>-20.2959</v>
       </c>
       <c r="H14" t="n">
-        <v>37.8009</v>
+        <v>37.9737</v>
       </c>
       <c r="I14" t="n">
-        <v>-58.4718</v>
+        <v>-58.2687</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5684</v>
+        <v>-1.519500000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>16.0113</v>
+        <v>13.7991</v>
       </c>
       <c r="L14" t="n">
-        <v>-14.4441</v>
+        <v>-15.3186</v>
       </c>
       <c r="M14" t="n">
-        <v>-22.2396</v>
+        <v>-18.7764</v>
       </c>
       <c r="N14" t="n">
-        <v>21.7878</v>
+        <v>24.1743</v>
       </c>
       <c r="O14" t="n">
-        <v>-44.0289</v>
+        <v>-42.9504</v>
       </c>
       <c r="P14" t="n">
-        <v>-44.9967</v>
+        <v>-45.4674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-145.3749</v>
+        <v>-146.8965</v>
       </c>
       <c r="R14" t="n">
-        <v>100.3791</v>
+        <v>101.4273</v>
       </c>
       <c r="S14" t="n">
-        <v>2.162100000000001</v>
+        <v>2.335500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>31.8843</v>
+        <v>29.4717</v>
       </c>
       <c r="U14" t="n">
-        <v>-29.7201</v>
+        <v>-27.1368</v>
       </c>
       <c r="V14" t="n">
-        <v>20.2629</v>
+        <v>20.0367</v>
       </c>
       <c r="W14" t="n">
-        <v>63.99839999999999</v>
+        <v>63.03660000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-43.7358</v>
+        <v>-43.0005</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1139</v>
+        <v>6.894</v>
       </c>
       <c r="E2" t="n">
-        <v>18.099</v>
+        <v>2.7688</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.985099999999999</v>
+        <v>4.1252</v>
       </c>
       <c r="G2" t="n">
-        <v>14.1642</v>
+        <v>5.8945</v>
       </c>
       <c r="H2" t="n">
-        <v>19.6155</v>
+        <v>3.1291</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.4519</v>
+        <v>2.7654</v>
       </c>
       <c r="J2" t="n">
-        <v>15.3552</v>
+        <v>4.1199</v>
       </c>
       <c r="K2" t="n">
-        <v>10.9191</v>
+        <v>1.3884</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4364</v>
+        <v>2.7313</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.191299999999999</v>
+        <v>1.7747</v>
       </c>
       <c r="N2" t="n">
-        <v>8.6967</v>
+        <v>1.7405</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.887699999999999</v>
+        <v>0.0341999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.197</v>
+        <v>2.754</v>
       </c>
       <c r="Q2" t="n">
-        <v>-14.6898</v>
+        <v>-2.5244</v>
       </c>
       <c r="R2" t="n">
-        <v>10.4925</v>
+        <v>5.2785</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3415</v>
+        <v>-1.5152</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0243</v>
+        <v>1.1109</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6828000000000001</v>
+        <v>-2.6261</v>
       </c>
       <c r="V2" t="n">
-        <v>3.8052</v>
+        <v>-0.2392</v>
       </c>
       <c r="W2" t="n">
-        <v>14.409</v>
+        <v>0.06240000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.6035</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>15.378</v>
+        <v>6.040500000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>9.0093</v>
+        <v>1.6162</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3687</v>
+        <v>4.424</v>
       </c>
       <c r="G3" t="n">
-        <v>16.0614</v>
+        <v>9.292100000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>16.4619</v>
+        <v>6.9308</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4005000000000002</v>
+        <v>2.3611</v>
       </c>
       <c r="J3" t="n">
-        <v>12.6105</v>
+        <v>6.352799999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>12.2514</v>
+        <v>4.214399999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3588000000000002</v>
+        <v>2.1385</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4509</v>
+        <v>2.939</v>
       </c>
       <c r="N3" t="n">
-        <v>4.210500000000001</v>
+        <v>2.7164</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7596000000000001</v>
+        <v>0.2226</v>
       </c>
       <c r="P3" t="n">
-        <v>4.197</v>
+        <v>-3.9015</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.0936</v>
+        <v>-7.1144</v>
       </c>
       <c r="R3" t="n">
-        <v>13.2903</v>
+        <v>3.213</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6999000000000002</v>
+        <v>0.3326</v>
       </c>
       <c r="T3" t="n">
-        <v>4.257</v>
+        <v>-0.3274000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.5568</v>
+        <v>0.6597</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.5803</v>
+        <v>0.3173</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2357</v>
+        <v>2.705</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.816000000000001</v>
+        <v>-2.3877</v>
       </c>
     </row>
     <row r="4">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8.551500000000001</v>
+        <v>3.842200000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4623</v>
+        <v>-0.3840999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>8.0892</v>
+        <v>4.226</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.8111</v>
+        <v>-3.4428</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.7583</v>
+        <v>0.9160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.0528</v>
+        <v>-4.3587</v>
       </c>
       <c r="J4" t="n">
-        <v>-13.2795</v>
+        <v>-5.4496</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.9834</v>
+        <v>-1.8653</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2961000000000009</v>
+        <v>-3.5842</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5316000000000001</v>
+        <v>2.0068</v>
       </c>
       <c r="N4" t="n">
-        <v>5.225099999999999</v>
+        <v>2.7813</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.7567</v>
+        <v>-0.7743</v>
       </c>
       <c r="P4" t="n">
-        <v>6.9951</v>
+        <v>5.049</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.394</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>15.3891</v>
+        <v>5.049</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5931000000000002</v>
+        <v>-0.8592</v>
       </c>
       <c r="T4" t="n">
-        <v>5.7141</v>
+        <v>1.5179</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.1207</v>
+        <v>-2.3771</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7747</v>
+        <v>3.0952</v>
       </c>
       <c r="W4" t="n">
-        <v>16.4217</v>
+        <v>3.5478</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6476</v>
+        <v>-0.4527</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0691</v>
+        <v>2.3711</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6976</v>
+        <v>0.1640000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>4.767</v>
+        <v>2.2071</v>
       </c>
       <c r="G5" t="n">
-        <v>1.934100000000001</v>
+        <v>1.4226</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.1617</v>
+        <v>6.8392</v>
       </c>
       <c r="I5" t="n">
-        <v>5.0961</v>
+        <v>-5.4163</v>
       </c>
       <c r="J5" t="n">
-        <v>5.693700000000001</v>
+        <v>0.8914</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.3628</v>
+        <v>6.3216</v>
       </c>
       <c r="L5" t="n">
-        <v>8.0562</v>
+        <v>-5.4302</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7593</v>
+        <v>0.5313999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7991999999999999</v>
+        <v>0.5176000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9604</v>
+        <v>0.01389999999999991</v>
       </c>
       <c r="P5" t="n">
-        <v>-6.2955</v>
+        <v>2.295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-16.7883</v>
+        <v>-2.5244</v>
       </c>
       <c r="R5" t="n">
-        <v>10.4925</v>
+        <v>4.8195</v>
       </c>
       <c r="S5" t="n">
-        <v>5.781</v>
+        <v>-2.6575</v>
       </c>
       <c r="T5" t="n">
-        <v>7.1613</v>
+        <v>0.4133</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3803</v>
+        <v>-3.0708</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6497999999999999</v>
+        <v>1.3109</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2357</v>
+        <v>1.3837</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5859</v>
+        <v>-0.0728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5004</v>
+        <v>1.9246</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-2.8676</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5004</v>
+        <v>4.7923</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5004</v>
+        <v>-4.877</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5004</v>
+        <v>2.9245</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-7.8016</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-6.3133</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.1886999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-6.1246</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5004</v>
+        <v>1.4363</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5004</v>
+        <v>3.1135</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.677</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.9835</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.7539</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>5.737500000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.01570000000000005</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.5699</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-1.5543</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.8026</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.6298</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3096</v>
+        <v>1.3779</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5982</v>
+        <v>-0.2211999999999998</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7117</v>
+        <v>1.599</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3759</v>
+        <v>2.4653</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.9402</v>
+        <v>0.1781999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5643</v>
+        <v>2.2871</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1442</v>
+        <v>3.089</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4742</v>
+        <v>1.0246</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3303</v>
+        <v>2.0645</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2317</v>
+        <v>-0.6238</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4657</v>
+        <v>-0.8466</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2343</v>
+        <v>0.2225999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0985</v>
+        <v>-3.672</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-6.1965</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0985</v>
+        <v>2.5245</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7578</v>
+        <v>2.6575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1341</v>
+        <v>2.5845</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6234</v>
+        <v>0.07310000000000005</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.79</v>
+        <v>-0.07290000000000002</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4119</v>
+        <v>0.3017</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.2019</v>
+        <v>-0.3746</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.262</v>
+        <v>-0.341</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.494899999999999</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7668000000000001</v>
+        <v>-0.341</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6025</v>
+        <v>-0.341</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6224999999999997</v>
+        <v>-0.341</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2253</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9107</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7801</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8691</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6917999999999997</v>
+        <v>-0.341</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.4026</v>
+        <v>-0.341</v>
       </c>
       <c r="O8" t="n">
-        <v>4.0938</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6996</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.197</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.8966</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.3619</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.2089</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.1533</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.2019</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.1006</v>
+        <v>-1.6793</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.9838</v>
+        <v>-1.1886</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8835</v>
+        <v>-0.4906</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9616</v>
+        <v>-1.3143</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8508</v>
+        <v>-3.1232</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1108</v>
+        <v>1.8089</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.9008</v>
+        <v>-0.5026999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3754</v>
+        <v>-0.5596999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.5254</v>
+        <v>0.05700000000000005</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9392</v>
+        <v>-0.8116000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5243</v>
+        <v>-2.5633</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4149</v>
+        <v>1.7517</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.5959</v>
+        <v>1.6065</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.995100000000001</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3989</v>
+        <v>1.6065</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4569</v>
+        <v>-0.8892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0882</v>
+        <v>-0.6859000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5451</v>
+        <v>-0.2035</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.082</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="10">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.434200000000001</v>
+        <v>-2.1457</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.947699999999999</v>
+        <v>-2.1871</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4865</v>
+        <v>0.0414000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5855</v>
+        <v>-0.7699</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.2895</v>
+        <v>-1.9625</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7043</v>
+        <v>1.1926</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7971000000000004</v>
+        <v>0.009400000000000075</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3473</v>
+        <v>-0.2868999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5502</v>
+        <v>0.2965</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7884</v>
+        <v>-0.7794999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9422</v>
+        <v>-1.6756</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1541</v>
+        <v>0.8961</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.394</v>
+        <v>-4.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.1921</v>
+        <v>-5.967</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7981</v>
+        <v>1.377</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3226</v>
+        <v>1.6795</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5853</v>
+        <v>0.0716</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9079</v>
+        <v>1.6077</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7773000000000003</v>
+        <v>1.5346</v>
       </c>
       <c r="W10" t="n">
-        <v>5.6268</v>
+        <v>3.6987</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.4041</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.6591</v>
+        <v>-2.5107</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.110100000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5489999999999997</v>
+        <v>-2.2727</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.644</v>
+        <v>-2.4426</v>
       </c>
       <c r="H11" t="n">
-        <v>14.8794</v>
+        <v>-2.5741</v>
       </c>
       <c r="I11" t="n">
-        <v>-22.5234</v>
+        <v>0.1314</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6874</v>
+        <v>-0.8578</v>
       </c>
       <c r="K11" t="n">
-        <v>9.713700000000001</v>
+        <v>-0.9688999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.4011</v>
+        <v>0.1113</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.9566</v>
+        <v>-1.5848</v>
       </c>
       <c r="N11" t="n">
-        <v>5.165699999999999</v>
+        <v>-1.605</v>
       </c>
       <c r="O11" t="n">
-        <v>-10.122</v>
+        <v>0.02039999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0985</v>
+        <v>0.918</v>
       </c>
       <c r="Q11" t="n">
-        <v>-14.6898</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>12.5907</v>
+        <v>0.918</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.7807</v>
+        <v>0.8762999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2287</v>
+        <v>0.3182</v>
       </c>
       <c r="U11" t="n">
-        <v>-8.0097</v>
+        <v>0.5581</v>
       </c>
       <c r="V11" t="n">
-        <v>5.864699999999999</v>
+        <v>-1.8624</v>
       </c>
       <c r="W11" t="n">
-        <v>6.0387</v>
+        <v>0.3018</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.174</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.4547</v>
+        <v>-2.6567</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.7809</v>
+        <v>-3.9168</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6735000000000004</v>
+        <v>1.2601</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2227</v>
+        <v>-0.9837</v>
       </c>
       <c r="H12" t="n">
-        <v>10.3113</v>
+        <v>-0.2899</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9116999999999997</v>
+        <v>-0.6939</v>
       </c>
       <c r="J12" t="n">
-        <v>15.6543</v>
+        <v>-1.5657</v>
       </c>
       <c r="K12" t="n">
-        <v>8.571000000000002</v>
+        <v>-0.7573</v>
       </c>
       <c r="L12" t="n">
-        <v>7.082999999999999</v>
+        <v>-0.8084</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.4316</v>
+        <v>0.582</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7403</v>
+        <v>0.4674</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.171600000000001</v>
+        <v>0.1146</v>
       </c>
       <c r="P12" t="n">
-        <v>-29.3793</v>
+        <v>-1.836</v>
       </c>
       <c r="Q12" t="n">
-        <v>-41.2707</v>
+        <v>-2.295</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8914</v>
+        <v>0.459</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3595</v>
+        <v>0.163</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8098</v>
+        <v>-0.0561</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.1693</v>
+        <v>0.2191</v>
       </c>
       <c r="V12" t="n">
-        <v>1.061699999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>4.0257</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.7851</v>
+        <v>-5.7131</v>
       </c>
       <c r="E13" t="n">
-        <v>-28.8648</v>
+        <v>-7.2608</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9206</v>
+        <v>1.5476</v>
       </c>
       <c r="G13" t="n">
-        <v>-36.4023</v>
+        <v>2.4761</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.171</v>
+        <v>0.1759</v>
       </c>
       <c r="I13" t="n">
-        <v>-33.231</v>
+        <v>2.3003</v>
       </c>
       <c r="J13" t="n">
-        <v>-29.9349</v>
+        <v>2.9093</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.8931</v>
+        <v>0.9663999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.0418</v>
+        <v>1.9429</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.4674</v>
+        <v>-0.4331</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7218</v>
+        <v>-0.7905</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.1895</v>
+        <v>0.3575999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4974</v>
+        <v>-7.3439</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.5861</v>
+        <v>-11.9337</v>
       </c>
       <c r="R13" t="n">
-        <v>16.0887</v>
+        <v>4.59</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8848</v>
+        <v>-0.5332</v>
       </c>
       <c r="T13" t="n">
-        <v>7.024800000000001</v>
+        <v>1.0718</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1403</v>
+        <v>-1.6052</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2301</v>
+        <v>-0.3120999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>13.6314</v>
+        <v>0.6919000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.4016</v>
+        <v>-1.004</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-43.39320000000001</v>
+        <v>7.403799999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-55.9074</v>
+        <v>-13.7151</v>
       </c>
       <c r="F14" t="n">
-        <v>12.5148</v>
+        <v>21.1184</v>
       </c>
       <c r="G14" t="n">
-        <v>-20.2959</v>
+        <v>7.379300000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>37.9737</v>
+        <v>12.803</v>
       </c>
       <c r="I14" t="n">
-        <v>-58.2687</v>
+        <v>-5.423699999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.519500000000001</v>
+        <v>2.682699999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>13.7991</v>
+        <v>9.288600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-15.3186</v>
+        <v>-6.605400000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.7764</v>
+        <v>4.696400000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>24.1743</v>
+        <v>3.514700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-42.9504</v>
+        <v>1.1824</v>
       </c>
       <c r="P14" t="n">
-        <v>-45.4674</v>
+        <v>-5.737399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-146.8965</v>
+        <v>-41.3093</v>
       </c>
       <c r="R14" t="n">
-        <v>101.4273</v>
+        <v>35.5725</v>
       </c>
       <c r="S14" t="n">
-        <v>2.335500000000001</v>
+        <v>-0.7297000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>29.4717</v>
+        <v>7.588699999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-27.1368</v>
+        <v>-8.319300000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>20.0367</v>
+        <v>6.491999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>63.03660000000001</v>
+        <v>17.3228</v>
       </c>
       <c r="X14" t="n">
-        <v>-43.0005</v>
+        <v>-10.8308</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.894</v>
+        <v>6.8303</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7688</v>
+        <v>2.1053</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1252</v>
+        <v>4.725</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8945</v>
+        <v>5.792899999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1291</v>
+        <v>3.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7654</v>
+        <v>2.7501</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1199</v>
+        <v>3.7892</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3884</v>
+        <v>1.1269</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7313</v>
+        <v>2.6623</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7747</v>
+        <v>2.0037</v>
       </c>
       <c r="N2" t="n">
-        <v>1.7405</v>
+        <v>1.9159</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0341999999999999</v>
+        <v>0.08779999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>2.754</v>
+        <v>2.8076</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R2" t="n">
-        <v>5.2785</v>
+        <v>5.3813</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5152</v>
+        <v>-1.5066</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1109</v>
+        <v>0.8847</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.6261</v>
+        <v>-2.3916</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2392</v>
+        <v>-0.2635</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06240000000000001</v>
+        <v>0.005299999999999971</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3018</v>
+        <v>-0.2686</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6.040500000000001</v>
+        <v>5.9314</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6162</v>
+        <v>1.0319</v>
       </c>
       <c r="F3" t="n">
-        <v>4.424</v>
+        <v>4.8995</v>
       </c>
       <c r="G3" t="n">
-        <v>9.292100000000001</v>
+        <v>9.2079</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9308</v>
+        <v>6.871700000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3611</v>
+        <v>2.3362</v>
       </c>
       <c r="J3" t="n">
-        <v>6.352799999999999</v>
+        <v>6.1395</v>
       </c>
       <c r="K3" t="n">
-        <v>4.214399999999999</v>
+        <v>4.0628</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1385</v>
+        <v>2.0767</v>
       </c>
       <c r="M3" t="n">
-        <v>2.939</v>
+        <v>3.0685</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7164</v>
+        <v>2.8089</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2226</v>
+        <v>0.2595000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.9015</v>
+        <v>-3.9776</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.1144</v>
+        <v>-7.2531</v>
       </c>
       <c r="R3" t="n">
-        <v>3.213</v>
+        <v>3.2757</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3326</v>
+        <v>0.3581</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3274000000000001</v>
+        <v>-0.5147</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6597</v>
+        <v>0.8726</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3173</v>
+        <v>0.343</v>
       </c>
       <c r="W3" t="n">
-        <v>2.705</v>
+        <v>2.6603</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3877</v>
+        <v>-2.3173</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.842200000000001</v>
+        <v>3.858</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3840999999999999</v>
+        <v>-0.9062</v>
       </c>
       <c r="F4" t="n">
-        <v>4.226</v>
+        <v>4.764200000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.4428</v>
+        <v>-3.4853</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9160000000000001</v>
+        <v>0.8386999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.3587</v>
+        <v>-4.324</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.4496</v>
+        <v>-5.686500000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.8653</v>
+        <v>-2.0824</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.5842</v>
+        <v>-3.6041</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0068</v>
+        <v>2.2012</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7813</v>
+        <v>2.921</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7743</v>
+        <v>-0.7198</v>
       </c>
       <c r="P4" t="n">
-        <v>5.049</v>
+        <v>5.1473</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5.049</v>
+        <v>5.1473</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8592</v>
+        <v>-0.8621</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5179</v>
+        <v>1.3194</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.3771</v>
+        <v>-2.1813</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0952</v>
+        <v>3.0581</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5478</v>
+        <v>3.461</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4527</v>
+        <v>-0.4029</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3711</v>
+        <v>2.2656</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1640000000000001</v>
+        <v>-0.3628999999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2071</v>
+        <v>2.6286</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4226</v>
+        <v>1.3722</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8392</v>
+        <v>6.7536</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.4163</v>
+        <v>-5.381600000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8914</v>
+        <v>0.6574</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3216</v>
+        <v>6.0941</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.4302</v>
+        <v>-5.4367</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5313999999999999</v>
+        <v>0.7146</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5176000000000001</v>
+        <v>0.6595</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01389999999999991</v>
+        <v>0.05509999999999993</v>
       </c>
       <c r="P5" t="n">
-        <v>2.295</v>
+        <v>2.3398</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R5" t="n">
-        <v>4.8195</v>
+        <v>4.9135</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.6575</v>
+        <v>-2.7242</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4133</v>
+        <v>0.2206</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.0708</v>
+        <v>-2.9448</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3109</v>
+        <v>1.2781</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3837</v>
+        <v>1.3328</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0728</v>
+        <v>-0.0548</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9246</v>
+        <v>2.0428</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8676</v>
+        <v>-3.4019</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7923</v>
+        <v>5.4446</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.877</v>
+        <v>-4.8368</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9245</v>
+        <v>2.9625</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.8016</v>
+        <v>-7.7992</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.3133</v>
+        <v>-6.4721</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1886999999999999</v>
+        <v>-0.2862999999999998</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.1246</v>
+        <v>-6.1858</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4363</v>
+        <v>1.6351</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1135</v>
+        <v>3.2487</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.677</v>
+        <v>-1.6134</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9835</v>
+        <v>3.0415</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7539</v>
+        <v>-2.8077</v>
       </c>
       <c r="R6" t="n">
-        <v>5.737500000000001</v>
+        <v>5.8492</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01570000000000005</v>
+        <v>0.03900000000000015</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5699</v>
+        <v>1.3527</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5543</v>
+        <v>-1.3137</v>
       </c>
       <c r="V6" t="n">
-        <v>3.8026</v>
+        <v>3.7988</v>
       </c>
       <c r="W6" t="n">
-        <v>4.6298</v>
+        <v>4.525</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8272</v>
+        <v>-0.7262</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3779</v>
+        <v>1.3383</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2211999999999998</v>
+        <v>-0.7822999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.599</v>
+        <v>2.1206</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4653</v>
+        <v>2.4488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1781999999999999</v>
+        <v>0.1857</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2871</v>
+        <v>2.2631</v>
       </c>
       <c r="J7" t="n">
-        <v>3.089</v>
+        <v>2.8578</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0246</v>
+        <v>0.8543999999999998</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0645</v>
+        <v>2.0034</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6238</v>
+        <v>-0.4091</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8466</v>
+        <v>-0.6687000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2225999999999999</v>
+        <v>0.2596000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.672</v>
+        <v>-3.7435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.1965</v>
+        <v>-6.3172</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5245</v>
+        <v>2.5737</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6575</v>
+        <v>2.6879</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5845</v>
+        <v>2.4085</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07310000000000005</v>
+        <v>0.2794</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.07290000000000002</v>
+        <v>-0.0547</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3746</v>
+        <v>-0.3234</v>
       </c>
     </row>
     <row r="8">
@@ -1033,19 +1033,19 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.341</v>
+        <v>-0.332</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.341</v>
+        <v>-0.332</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.341</v>
+        <v>-0.332</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.341</v>
+        <v>-0.332</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.341</v>
+        <v>-0.332</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.341</v>
+        <v>-0.332</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6793</v>
+        <v>-1.5189</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1886</v>
+        <v>-1.3732</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4906</v>
+        <v>-0.1456999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3143</v>
+        <v>-1.2042</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1232</v>
+        <v>-3.0002</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8089</v>
+        <v>1.796</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5026999999999999</v>
+        <v>-0.5568</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5596999999999999</v>
+        <v>-0.5861</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05700000000000005</v>
+        <v>0.02929999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8116000000000001</v>
+        <v>-0.6474000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5633</v>
+        <v>-2.4141</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7517</v>
+        <v>1.7667</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8892</v>
+        <v>-0.8883999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6859000000000001</v>
+        <v>-0.8165</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2035</v>
+        <v>-0.07190000000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1457</v>
+        <v>-2.1547</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1871</v>
+        <v>-2.5424</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0414000000000001</v>
+        <v>0.3876999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7699</v>
+        <v>-0.6776</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9625</v>
+        <v>-1.8865</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1926</v>
+        <v>1.2089</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009400000000000075</v>
+        <v>-0.02760000000000007</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2868999999999999</v>
+        <v>-0.3204</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2965</v>
+        <v>0.2928</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7794999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6756</v>
+        <v>-1.5661</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8961</v>
+        <v>0.9160999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.59</v>
+        <v>-4.679399999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.967</v>
+        <v>-6.0832</v>
       </c>
       <c r="R10" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6795</v>
+        <v>1.7354</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0716</v>
+        <v>-0.02689999999999992</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6077</v>
+        <v>1.7622</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5346</v>
+        <v>1.4671</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6987</v>
+        <v>3.5953</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5107</v>
+        <v>-2.4157</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2379</v>
+        <v>-0.3446</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2727</v>
+        <v>-2.0713</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4426</v>
+        <v>-2.3722</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5741</v>
+        <v>-2.5146</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1314</v>
+        <v>0.1426</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8578</v>
+        <v>-0.8746</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9688999999999999</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1113</v>
+        <v>0.1098</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5848</v>
+        <v>-1.4974</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.605</v>
+        <v>-1.5302</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02039999999999999</v>
+        <v>0.0326</v>
       </c>
       <c r="P11" t="n">
-        <v>0.918</v>
+        <v>0.9358</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.918</v>
+        <v>0.9358</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8762999999999999</v>
+        <v>0.8801000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3182</v>
+        <v>0.2616000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5581</v>
+        <v>0.6185</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8624</v>
+        <v>-1.8596</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3018</v>
+        <v>0.2686</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6567</v>
+        <v>-2.6662</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9168</v>
+        <v>-3.9848</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2601</v>
+        <v>1.3186</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9837</v>
+        <v>-0.9714</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2899</v>
+        <v>-0.2822</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6939</v>
+        <v>-0.6891</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5657</v>
+        <v>-1.5656</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7573</v>
+        <v>-0.7579</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="M12" t="n">
-        <v>0.582</v>
+        <v>0.5942</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4674</v>
+        <v>0.4756</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1146</v>
+        <v>0.1186</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R12" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S12" t="n">
-        <v>0.163</v>
+        <v>0.1769</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0561</v>
+        <v>-0.0795</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2191</v>
+        <v>0.2564</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7131</v>
+        <v>-5.8392</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.2608</v>
+        <v>-8.0159</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5476</v>
+        <v>2.1767</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4761</v>
+        <v>2.4744</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1759</v>
+        <v>0.2163</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3003</v>
+        <v>2.2581</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9093</v>
+        <v>2.6246</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9663999999999999</v>
+        <v>0.7771999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9429</v>
+        <v>1.8474</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4331</v>
+        <v>-0.1502</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7905</v>
+        <v>-0.5610999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3575999999999999</v>
+        <v>0.4109</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.3439</v>
+        <v>-7.4871</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.9337</v>
+        <v>-12.1666</v>
       </c>
       <c r="R13" t="n">
-        <v>4.59</v>
+        <v>4.6795</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5332</v>
+        <v>-0.5081</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0718</v>
+        <v>0.8596999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6052</v>
+        <v>-1.368</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3120999999999998</v>
+        <v>-0.3181</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6919000000000001</v>
+        <v>0.6664000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.004</v>
+        <v>-0.9846</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>7.403799999999998</v>
+        <v>7.339700000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.7151</v>
+        <v>-18.577</v>
       </c>
       <c r="F14" t="n">
-        <v>21.1184</v>
+        <v>25.9165</v>
       </c>
       <c r="G14" t="n">
-        <v>7.379300000000002</v>
+        <v>7.416699999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>12.803</v>
+        <v>12.8558</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.423699999999998</v>
+        <v>-5.4389</v>
       </c>
       <c r="J14" t="n">
-        <v>2.682699999999999</v>
+        <v>0.8852999999999984</v>
       </c>
       <c r="K14" t="n">
-        <v>9.288600000000001</v>
+        <v>7.897899999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.605400000000001</v>
+        <v>-7.012600000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>4.696400000000001</v>
+        <v>6.5312</v>
       </c>
       <c r="N14" t="n">
-        <v>3.514700000000001</v>
+        <v>4.957399999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1824</v>
+        <v>1.5737</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.737399999999999</v>
+        <v>-5.849599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-41.3093</v>
+        <v>-42.11490000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>35.5725</v>
+        <v>36.2655</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7297000000000003</v>
+        <v>-0.6119999999999994</v>
       </c>
       <c r="T14" t="n">
-        <v>7.588699999999999</v>
+        <v>5.869599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.319300000000002</v>
+        <v>-6.482200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>6.491999999999999</v>
+        <v>6.385099999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>17.3228</v>
+        <v>16.7833</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.8308</v>
+        <v>-10.3983</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8303</v>
+        <v>5.3146</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1053</v>
+        <v>6.1334</v>
       </c>
       <c r="F2" t="n">
-        <v>4.725</v>
+        <v>-0.8186000000000004</v>
       </c>
       <c r="G2" t="n">
-        <v>5.792899999999999</v>
+        <v>4.6623</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0428</v>
+        <v>6.4515</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7501</v>
+        <v>-1.7891</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7892</v>
+        <v>5.4385</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1269</v>
+        <v>3.7876</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6623</v>
+        <v>1.6509</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0037</v>
+        <v>-0.7759999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9159</v>
+        <v>2.664</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08779999999999999</v>
+        <v>-3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8076</v>
+        <v>-1.3925</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5737</v>
+        <v>-4.8735</v>
       </c>
       <c r="R2" t="n">
-        <v>5.3813</v>
+        <v>3.4811</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5066</v>
+        <v>0.7821999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8847</v>
+        <v>0.7457</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.3916</v>
+        <v>0.03659999999999997</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2635</v>
+        <v>1.2625</v>
       </c>
       <c r="W2" t="n">
-        <v>0.005299999999999971</v>
+        <v>4.8227</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2686</v>
+        <v>-3.5603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9314</v>
+        <v>5.0883</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0319</v>
+        <v>3.1028</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8995</v>
+        <v>1.9857</v>
       </c>
       <c r="G3" t="n">
-        <v>9.2079</v>
+        <v>5.305099999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>6.871700000000001</v>
+        <v>5.4615</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3362</v>
+        <v>-0.1563000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1395</v>
+        <v>4.5873</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0628</v>
+        <v>4.3276</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0767</v>
+        <v>0.2597</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0685</v>
+        <v>0.7179000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8089</v>
+        <v>1.134</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2595000000000001</v>
+        <v>-0.4159999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.9776</v>
+        <v>1.3924</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.2531</v>
+        <v>-3.0169</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2757</v>
+        <v>4.4094</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3581</v>
+        <v>0.2515999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5147</v>
+        <v>1.1083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8726</v>
+        <v>-0.8569</v>
       </c>
       <c r="V3" t="n">
-        <v>0.343</v>
+        <v>-1.8607</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6603</v>
+        <v>0.424</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3173</v>
+        <v>-2.2847</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.858</v>
+        <v>2.9863</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9062</v>
+        <v>0.4465000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>4.764200000000001</v>
+        <v>2.5398</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.4853</v>
+        <v>-4.4906</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8386999999999998</v>
+        <v>-2.4669</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.324</v>
+        <v>-2.0236</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.686500000000001</v>
+        <v>-3.8539</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0824</v>
+        <v>-3.9228</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.6041</v>
+        <v>0.06870000000000021</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2012</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>2.921</v>
+        <v>1.4559</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7198</v>
+        <v>-2.0924</v>
       </c>
       <c r="P4" t="n">
-        <v>5.1473</v>
+        <v>2.3207</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.7849</v>
       </c>
       <c r="R4" t="n">
-        <v>5.1473</v>
+        <v>5.1055</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8621</v>
+        <v>0.2215000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3194</v>
+        <v>1.5855</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.1813</v>
+        <v>-1.364</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0581</v>
+        <v>4.9346</v>
       </c>
       <c r="W4" t="n">
-        <v>3.461</v>
+        <v>5.4999</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4029</v>
+        <v>-0.5653</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2656</v>
+        <v>0.5982</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3628999999999998</v>
+        <v>-0.8691999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6286</v>
+        <v>1.4672</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3722</v>
+        <v>0.5367999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7536</v>
+        <v>-1.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.381600000000001</v>
+        <v>1.6534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6574</v>
+        <v>2.2294</v>
       </c>
       <c r="K5" t="n">
-        <v>6.0941</v>
+        <v>-0.5760000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.4367</v>
+        <v>2.8053</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7146</v>
+        <v>-1.6926</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6595</v>
+        <v>-0.5406</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05509999999999993</v>
+        <v>-1.1519</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3398</v>
+        <v>-2.0886</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5737</v>
+        <v>-5.5697</v>
       </c>
       <c r="R5" t="n">
-        <v>4.9135</v>
+        <v>3.4811</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.7242</v>
+        <v>1.9298</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2206</v>
+        <v>2.0473</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.9448</v>
+        <v>-0.1175</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2781</v>
+        <v>0.2202</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3328</v>
+        <v>0.424</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0548</v>
+        <v>-0.2037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0428</v>
+        <v>-0.1679</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.4019</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4446</v>
+        <v>-0.1679</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.8368</v>
+        <v>-0.1679</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9625</v>
+        <v>-0.1679</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.7992</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.4721</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2862999999999998</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.1858</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6351</v>
+        <v>-0.1679</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2487</v>
+        <v>-0.1679</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6134</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0415</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8077</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>5.8492</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03900000000000015</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3527</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3137</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.7988</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>4.525</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3383</v>
+        <v>-1.1803</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7822999999999999</v>
+        <v>-0.234</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1206</v>
+        <v>-0.9463000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4488</v>
+        <v>-1.1911</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1857</v>
+        <v>-1.3406</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2631</v>
+        <v>0.1495</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8578</v>
+        <v>-0.3533</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8543999999999998</v>
+        <v>-0.4637</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0034</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4091</v>
+        <v>-0.8378</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6687000000000001</v>
+        <v>-0.8768</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2596000000000001</v>
+        <v>0.0391</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.7435</v>
+        <v>0.6962</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.3172</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5737</v>
+        <v>0.6962</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6879</v>
+        <v>0.2449999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4085</v>
+        <v>-0.02200000000000002</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2794</v>
+        <v>0.2669</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0547</v>
+        <v>-0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2686</v>
+        <v>0.1413</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3234</v>
+        <v>-1.0717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.332</v>
+        <v>-1.8727</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-1.5261</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.332</v>
+        <v>-0.3465</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.332</v>
+        <v>0.7136999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.332</v>
+        <v>-0.3142</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.028</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.7291</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9636</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.2346</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.332</v>
+        <v>-0.01539999999999991</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.332</v>
+        <v>-1.2779</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.2625</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3924</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6245</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-1.7467</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.8628</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.8839000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.0717</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5189</v>
+        <v>-2.671</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3732</v>
+        <v>-3.9613</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1456999999999999</v>
+        <v>1.2904</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2042</v>
+        <v>-0.98</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0002</v>
+        <v>-0.2855</v>
       </c>
       <c r="I9" t="n">
-        <v>1.796</v>
+        <v>-0.6945</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5568</v>
+        <v>-1.5824</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5861</v>
+        <v>-0.766</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02929999999999999</v>
+        <v>-0.8164</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6474000000000001</v>
+        <v>0.6024</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.4141</v>
+        <v>0.4805</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7667</v>
+        <v>0.1219</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6378</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3207</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6378</v>
+        <v>0.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8883999999999999</v>
+        <v>0.1656</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8165</v>
+        <v>-0.0583</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07190000000000002</v>
+        <v>0.2238</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0641</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1547</v>
+        <v>-2.8611</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5424</v>
+        <v>-2.3134</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3876999999999999</v>
+        <v>-0.5478</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6776</v>
+        <v>-0.614</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8865</v>
+        <v>-1.1223</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2089</v>
+        <v>0.5083000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.02760000000000007</v>
+        <v>-0.2060999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3204</v>
+        <v>-0.3901000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2928</v>
+        <v>0.184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.65</v>
+        <v>-0.4080000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5661</v>
+        <v>-0.7323</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9160999999999999</v>
+        <v>0.3243</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.679399999999999</v>
+        <v>-2.7848</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.0832</v>
+        <v>-3.7131</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4038</v>
+        <v>0.9283</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7354</v>
+        <v>0.7909</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.02689999999999992</v>
+        <v>-0.2844</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7622</v>
+        <v>1.0753</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4671</v>
+        <v>-0.2532000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>3.5953</v>
+        <v>1.8902</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4157</v>
+        <v>-3.2768</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3446</v>
+        <v>-2.981</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0713</v>
+        <v>-0.2957999999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3722</v>
+        <v>-2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5146</v>
+        <v>4.8376</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1426</v>
+        <v>-7.4576</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8746</v>
+        <v>-0.6572000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9844000000000001</v>
+        <v>3.3211</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1098</v>
+        <v>-3.9784</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4974</v>
+        <v>-1.9627</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5302</v>
+        <v>1.5163</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0326</v>
+        <v>-3.4791</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9358</v>
+        <v>-0.6962000000000002</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.8735</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9358</v>
+        <v>4.1774</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8801000000000001</v>
+        <v>-1.9297</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2616000000000001</v>
+        <v>0.5182</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6185</v>
+        <v>-2.4479</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8596</v>
+        <v>1.9691</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2686</v>
+        <v>2.0316</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1282</v>
+        <v>-0.0624</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6662</v>
+        <v>-6.4471</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9848</v>
+        <v>-6.0659</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3186</v>
+        <v>-0.3811999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9714</v>
+        <v>3.6729</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2822</v>
+        <v>3.3233</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6891</v>
+        <v>0.3493999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5656</v>
+        <v>5.6254</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7579</v>
+        <v>3.0616</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8077</v>
+        <v>2.5638</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5942</v>
+        <v>-1.9526</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4756</v>
+        <v>0.2617</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1186</v>
+        <v>-2.2143</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8718</v>
+        <v>-9.747</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3397</v>
+        <v>-13.6923</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4679</v>
+        <v>3.9453</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1769</v>
+        <v>-0.7345</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0795</v>
+        <v>0.6465000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2564</v>
+        <v>-1.3811</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3616000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.3544</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.9928</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8392</v>
+        <v>-10.0278</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.0159</v>
+        <v>-9.2342</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1767</v>
+        <v>-0.7936000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4744</v>
+        <v>-11.8765</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2163</v>
+        <v>-1.1073</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2581</v>
+        <v>-10.7692</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6246</v>
+        <v>-9.297000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7771999999999999</v>
+        <v>-3.0716</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8474</v>
+        <v>-6.2254</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1502</v>
+        <v>-2.579499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5610999999999999</v>
+        <v>1.9643</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4109</v>
+        <v>-4.5438</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.4871</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.1666</v>
+        <v>-6.497999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>4.6795</v>
+        <v>5.3376</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5081</v>
+        <v>0.928</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8596999999999999</v>
+        <v>1.9913</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.368</v>
+        <v>-1.0633</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3181</v>
+        <v>2.081</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6664000000000001</v>
+        <v>4.5696</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9846</v>
+        <v>-2.4885</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>7.339700000000002</v>
+        <v>-14.5173</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.577</v>
+        <v>-17.5024</v>
       </c>
       <c r="F14" t="n">
-        <v>25.9165</v>
+        <v>2.9854</v>
       </c>
       <c r="G14" t="n">
-        <v>7.416699999999999</v>
+        <v>-7.0493</v>
       </c>
       <c r="H14" t="n">
-        <v>12.8558</v>
+        <v>12.1526</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.4389</v>
+        <v>-19.2017</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8852999999999984</v>
+        <v>2.659800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.897899999999999</v>
+        <v>6.2713</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.012600000000003</v>
+        <v>-3.612</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5312</v>
+        <v>-9.708799999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>4.957399999999999</v>
+        <v>5.8812</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5737</v>
+        <v>-15.5897</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.849599999999999</v>
+        <v>-15.0847</v>
       </c>
       <c r="Q14" t="n">
-        <v>-42.11490000000001</v>
+        <v>-48.73499999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>36.2655</v>
+        <v>33.6505</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6119999999999994</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>5.869599999999999</v>
+        <v>7.415299999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.482200000000001</v>
+        <v>-6.512</v>
       </c>
       <c r="V14" t="n">
-        <v>6.385099999999999</v>
+        <v>6.712999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>16.7833</v>
+        <v>21.1577</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.3983</v>
+        <v>-14.4445</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3146</v>
+        <v>5.3164</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1334</v>
+        <v>5.915900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8186000000000004</v>
+        <v>-0.5995999999999997</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6623</v>
+        <v>4.659899999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4515</v>
+        <v>6.455</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7891</v>
+        <v>-1.795</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4385</v>
+        <v>5.2562</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7876</v>
+        <v>3.684</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6509</v>
+        <v>1.5722</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7759999999999998</v>
+        <v>-0.5963000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>2.664</v>
+        <v>2.771</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.44</v>
+        <v>-3.3672</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.3925</v>
+        <v>-1.4026</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.8735</v>
+        <v>-4.9091</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4811</v>
+        <v>3.5065</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7821999999999999</v>
+        <v>0.7873</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7457</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03659999999999997</v>
+        <v>0.01069999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2625</v>
+        <v>1.2717</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8227</v>
+        <v>4.792199999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.5603</v>
+        <v>-3.5205</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0883</v>
+        <v>5.0872</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1028</v>
+        <v>2.8818</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9857</v>
+        <v>2.2056</v>
       </c>
       <c r="G3" t="n">
-        <v>5.305099999999999</v>
+        <v>5.292899999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4615</v>
+        <v>5.4391</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1563000000000001</v>
+        <v>-0.1462000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5873</v>
+        <v>4.3688</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3276</v>
+        <v>4.1696</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2597</v>
+        <v>0.1991999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7179000000000001</v>
+        <v>0.9241999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1.134</v>
+        <v>1.2696</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4159999999999999</v>
+        <v>-0.3453999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3924</v>
+        <v>1.4026</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0169</v>
+        <v>-3.0389</v>
       </c>
       <c r="R3" t="n">
-        <v>4.4094</v>
+        <v>4.4415</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2515999999999999</v>
+        <v>0.2515000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1083</v>
+        <v>1.1467</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8569</v>
+        <v>-0.8953</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8607</v>
+        <v>-1.8597</v>
       </c>
       <c r="W3" t="n">
-        <v>0.424</v>
+        <v>0.4053</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2847</v>
+        <v>-2.265</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9863</v>
+        <v>2.9497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4465000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5398</v>
+        <v>2.7817</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.4906</v>
+        <v>-4.5282</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.4669</v>
+        <v>-2.514</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0236</v>
+        <v>-2.0142</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.8539</v>
+        <v>-4.1145</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.9228</v>
+        <v>-4.111800000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06870000000000021</v>
+        <v>-0.002599999999999714</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.4137999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>1.4559</v>
+        <v>1.5979</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0924</v>
+        <v>-2.0117</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3207</v>
+        <v>2.3377</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7849</v>
+        <v>-2.8052</v>
       </c>
       <c r="R4" t="n">
-        <v>5.1055</v>
+        <v>5.1429</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2215000000000001</v>
+        <v>0.2207000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5855</v>
+        <v>1.6279</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.364</v>
+        <v>-1.4072</v>
       </c>
       <c r="V4" t="n">
-        <v>4.9346</v>
+        <v>4.919499999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>5.4999</v>
+        <v>5.4597</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5653</v>
+        <v>-0.5403</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5982</v>
+        <v>0.6445</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8691999999999999</v>
+        <v>-1.0498</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4672</v>
+        <v>1.6943</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5367999999999999</v>
+        <v>0.5911999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1166</v>
+        <v>-1.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6534</v>
+        <v>1.6671</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2294</v>
+        <v>2.0605</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5760000000000001</v>
+        <v>-0.6844999999999998</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8053</v>
+        <v>2.745</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6926</v>
+        <v>-1.4693</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5406</v>
+        <v>-0.3914</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1519</v>
+        <v>-1.0778</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0886</v>
+        <v>-2.1039</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.5697</v>
+        <v>-5.6105</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4811</v>
+        <v>3.5065</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9298</v>
+        <v>1.9426</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0473</v>
+        <v>2.0949</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1175</v>
+        <v>-0.1521999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2202</v>
+        <v>0.2145</v>
       </c>
       <c r="W5" t="n">
-        <v>0.424</v>
+        <v>0.4052</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2037</v>
+        <v>-0.1907</v>
       </c>
     </row>
     <row r="6">
@@ -877,19 +877,19 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1662</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1803</v>
+        <v>-1.1331</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.234</v>
+        <v>-0.246</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9463000000000001</v>
+        <v>-0.8870999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1911</v>
+        <v>-1.1519</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3406</v>
+        <v>-1.3174</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1495</v>
+        <v>0.1655</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3533</v>
+        <v>-0.3655</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4637</v>
+        <v>-0.4754</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1104</v>
+        <v>0.1098</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8378</v>
+        <v>-0.7864</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8768</v>
+        <v>-0.8419</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0391</v>
+        <v>0.05559999999999998</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6962</v>
+        <v>0.7013</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6962</v>
+        <v>0.7013</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2449999999999999</v>
+        <v>0.2473</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.02200000000000002</v>
+        <v>-0.01560000000000002</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2669</v>
+        <v>0.2629</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1413</v>
+        <v>0.1351</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8727</v>
+        <v>-1.8048</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5261</v>
+        <v>-1.5783</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3465</v>
+        <v>-0.2264</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7136999999999999</v>
+        <v>0.7891</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3142</v>
+        <v>-0.2555000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.028</v>
+        <v>1.0445</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7291</v>
+        <v>0.6804</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9636</v>
+        <v>0.9377000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2346</v>
+        <v>-0.2572</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01539999999999991</v>
+        <v>0.1087</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2779</v>
+        <v>-1.1931</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2625</v>
+        <v>1.3018</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2321</v>
+        <v>0.2338</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3924</v>
+        <v>-1.4026</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6245</v>
+        <v>1.6364</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7467</v>
+        <v>-1.7627</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8628</v>
+        <v>-0.8561</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8839000000000001</v>
+        <v>-0.9064999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.671</v>
+        <v>-2.6834</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9613</v>
+        <v>-3.9925</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2904</v>
+        <v>1.3092</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.98</v>
+        <v>-0.9786</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2855</v>
+        <v>-0.2826</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6945</v>
+        <v>-0.696</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5824</v>
+        <v>-1.5991</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.766</v>
+        <v>-0.7746</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8164</v>
+        <v>-0.8245</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6024</v>
+        <v>0.6204</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4805</v>
+        <v>0.492</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1219</v>
+        <v>0.1284</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8566</v>
+        <v>-1.8701</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3207</v>
+        <v>-2.3377</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4641</v>
+        <v>0.4675</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1656</v>
+        <v>0.1654</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0583</v>
+        <v>-0.0558</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2238</v>
+        <v>0.2212</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8611</v>
+        <v>-2.842</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3134</v>
+        <v>-2.385899999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5478</v>
+        <v>-0.4560999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.614</v>
+        <v>-0.5691999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1223</v>
+        <v>-1.1012</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5083000000000001</v>
+        <v>0.5321</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2060999999999999</v>
+        <v>-0.2357000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3901000000000001</v>
+        <v>-0.4187000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.184</v>
+        <v>0.1831</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4080000000000001</v>
+        <v>-0.3335</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7323</v>
+        <v>-0.6823</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3243</v>
+        <v>0.3489</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7848</v>
+        <v>-2.8052</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7131</v>
+        <v>-3.7403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9283</v>
+        <v>0.9351</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7909</v>
+        <v>0.7947</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2844</v>
+        <v>-0.2775</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0753</v>
+        <v>1.0722</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2532000000000001</v>
+        <v>-0.2623</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8902</v>
+        <v>1.8676</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1434</v>
+        <v>-2.1299</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2768</v>
+        <v>-3.2805</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.981</v>
+        <v>-3.1387</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2957999999999998</v>
+        <v>-0.1418999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.62</v>
+        <v>-2.5836</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8376</v>
+        <v>4.8704</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.4576</v>
+        <v>-7.4541</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6572000000000001</v>
+        <v>-0.7763000000000002</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3211</v>
+        <v>3.255</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.9784</v>
+        <v>-4.0312</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9627</v>
+        <v>-1.8074</v>
       </c>
       <c r="N11" t="n">
-        <v>1.5163</v>
+        <v>1.6154</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.4791</v>
+        <v>-3.4229</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6962000000000002</v>
+        <v>-0.7013</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8735</v>
+        <v>-4.9091</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1774</v>
+        <v>4.2077</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9297</v>
+        <v>-1.9426</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5182</v>
+        <v>0.5438999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.4479</v>
+        <v>-2.4867</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9691</v>
+        <v>1.947</v>
       </c>
       <c r="W11" t="n">
-        <v>2.0316</v>
+        <v>2.0026</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0624</v>
+        <v>-0.0556</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4471</v>
+        <v>-6.522600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0659</v>
+        <v>-6.3756</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3811999999999998</v>
+        <v>-0.147</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6729</v>
+        <v>3.6906</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3233</v>
+        <v>3.3616</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3493999999999999</v>
+        <v>0.3289</v>
       </c>
       <c r="J12" t="n">
-        <v>5.6254</v>
+        <v>5.4017</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0616</v>
+        <v>2.9328</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5638</v>
+        <v>2.469</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9526</v>
+        <v>-1.7111</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2617</v>
+        <v>0.429</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2143</v>
+        <v>-2.1401</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.747</v>
+        <v>-9.818200000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6923</v>
+        <v>-13.7921</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9453</v>
+        <v>3.974</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7345</v>
+        <v>-0.7446999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6465000000000001</v>
+        <v>0.6798000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3811</v>
+        <v>-1.4244</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3616000000000001</v>
+        <v>0.3495999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3544</v>
+        <v>1.3351</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9928</v>
+        <v>-0.9855</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.0278</v>
+        <v>-10.0943</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.2342</v>
+        <v>-9.545500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7936000000000001</v>
+        <v>-0.5488</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.8765</v>
+        <v>-11.9375</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1073</v>
+        <v>-1.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.7692</v>
+        <v>-10.8642</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.297000000000001</v>
+        <v>-9.569599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.0716</v>
+        <v>-3.1713</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.2254</v>
+        <v>-6.398300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.579499999999999</v>
+        <v>-2.368</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9643</v>
+        <v>2.098</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.5438</v>
+        <v>-4.465999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1604</v>
+        <v>-1.1688</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.497999999999999</v>
+        <v>-6.545500000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>5.3376</v>
+        <v>5.3767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.928</v>
+        <v>0.9377</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9913</v>
+        <v>2.0397</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0633</v>
+        <v>-1.1019</v>
       </c>
       <c r="V13" t="n">
-        <v>2.081</v>
+        <v>2.0743</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5696</v>
+        <v>4.5298</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4885</v>
+        <v>-2.4556</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.5173</v>
+        <v>-14.5291</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.5024</v>
+        <v>-19.3466</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9854</v>
+        <v>4.817700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.0493</v>
+        <v>-6.891500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>12.1526</v>
+        <v>12.34</v>
       </c>
       <c r="I14" t="n">
-        <v>-19.2017</v>
+        <v>-19.2316</v>
       </c>
       <c r="J14" t="n">
-        <v>2.659800000000001</v>
+        <v>1.106900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2713</v>
+        <v>5.3428</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.612</v>
+        <v>-4.235500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.708799999999998</v>
+        <v>-7.9987</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8812</v>
+        <v>6.997999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-15.5897</v>
+        <v>-14.9964</v>
       </c>
       <c r="P14" t="n">
-        <v>-15.0847</v>
+        <v>-15.1947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-48.73499999999999</v>
+        <v>-49.09100000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>33.6505</v>
+        <v>33.8961</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.8972000000000007</v>
       </c>
       <c r="T14" t="n">
-        <v>7.415299999999999</v>
+        <v>7.704600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.512</v>
+        <v>-6.807199999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>6.712999999999999</v>
+        <v>6.6598</v>
       </c>
       <c r="W14" t="n">
-        <v>21.1577</v>
+        <v>20.9326</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.4445</v>
+        <v>-14.2729</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3164</v>
+        <v>5.3098</v>
       </c>
       <c r="E2" t="n">
-        <v>5.915900000000001</v>
+        <v>5.8876</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5995999999999997</v>
+        <v>-0.5778999999999996</v>
       </c>
       <c r="G2" t="n">
-        <v>4.659899999999999</v>
+        <v>4.6523</v>
       </c>
       <c r="H2" t="n">
-        <v>6.455</v>
+        <v>6.4449</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.795</v>
+        <v>-1.7927</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2562</v>
+        <v>5.2613</v>
       </c>
       <c r="K2" t="n">
-        <v>3.684</v>
+        <v>3.6827</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5722</v>
+        <v>1.5786</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5963000000000003</v>
+        <v>-0.609</v>
       </c>
       <c r="N2" t="n">
-        <v>2.771</v>
+        <v>2.7623</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.3672</v>
+        <v>-3.3713</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4026</v>
+        <v>-1.4036</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.9091</v>
+        <v>-4.9129</v>
       </c>
       <c r="R2" t="n">
-        <v>3.5065</v>
+        <v>3.5092</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7873</v>
+        <v>0.7886000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7504000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01069999999999999</v>
+        <v>0.03820000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2717</v>
+        <v>1.2727</v>
       </c>
       <c r="W2" t="n">
-        <v>4.792199999999999</v>
+        <v>4.7889</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.5205</v>
+        <v>-3.5162</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0872</v>
+        <v>5.0825</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8818</v>
+        <v>2.8526</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2056</v>
+        <v>2.2299</v>
       </c>
       <c r="G3" t="n">
-        <v>5.292899999999999</v>
+        <v>5.2846</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4391</v>
+        <v>5.431699999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1462000000000001</v>
+        <v>-0.1470999999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3688</v>
+        <v>4.3748</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1696</v>
+        <v>4.1698</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1991999999999999</v>
+        <v>0.2051000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9241999999999999</v>
+        <v>0.9097999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2696</v>
+        <v>1.2619</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3453999999999999</v>
+        <v>-0.352</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4026</v>
+        <v>1.4036</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0389</v>
+        <v>-3.0413</v>
       </c>
       <c r="R3" t="n">
-        <v>4.4415</v>
+        <v>4.444900000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2515000000000001</v>
+        <v>0.2538000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1467</v>
+        <v>1.1159</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8953</v>
+        <v>-0.8621</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8597</v>
+        <v>-1.8596</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4053</v>
+        <v>0.4032</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.265</v>
+        <v>-2.2628</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9497</v>
+        <v>2.9594</v>
       </c>
       <c r="E4" t="n">
-        <v>0.168</v>
+        <v>0.1515</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7817</v>
+        <v>2.8079</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.5282</v>
+        <v>-4.5213</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.514</v>
+        <v>-2.5081</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0142</v>
+        <v>-2.0133</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.1145</v>
+        <v>-4.0932</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.111800000000001</v>
+        <v>-4.0977</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.002599999999999714</v>
+        <v>0.004599999999999937</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4137999999999999</v>
+        <v>-0.4283</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5979</v>
+        <v>1.5896</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0117</v>
+        <v>-2.0177</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3377</v>
+        <v>2.3395</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8052</v>
+        <v>-2.8074</v>
       </c>
       <c r="R4" t="n">
-        <v>5.1429</v>
+        <v>5.146800000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2207000000000001</v>
+        <v>0.2234</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6279</v>
+        <v>1.5967</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4072</v>
+        <v>-1.3732</v>
       </c>
       <c r="V4" t="n">
-        <v>4.919499999999999</v>
+        <v>4.9178</v>
       </c>
       <c r="W4" t="n">
-        <v>5.4597</v>
+        <v>5.4554</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5403</v>
+        <v>-0.5376</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6445</v>
+        <v>0.6418999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0498</v>
+        <v>-1.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6943</v>
+        <v>1.7219</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5911999999999998</v>
+        <v>0.5881000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0759</v>
+        <v>-1.0761</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6671</v>
+        <v>1.6642</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0605</v>
+        <v>2.0694</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6844999999999998</v>
+        <v>-0.6788999999999998</v>
       </c>
       <c r="L5" t="n">
-        <v>2.745</v>
+        <v>2.7484</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4693</v>
+        <v>-1.4813</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3914</v>
+        <v>-0.3972000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0778</v>
+        <v>-1.0842</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1039</v>
+        <v>-2.1056</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.6105</v>
+        <v>-5.6147</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5065</v>
+        <v>3.5092</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9426</v>
+        <v>1.9454</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0949</v>
+        <v>2.0622</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1521999999999999</v>
+        <v>-0.1167</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2145</v>
+        <v>0.2139</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4052</v>
+        <v>0.4032</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1907</v>
+        <v>-0.1892</v>
       </c>
     </row>
     <row r="6">
@@ -877,19 +877,19 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1331</v>
+        <v>-1.1337</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.246</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8870999999999999</v>
+        <v>-0.8812000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1519</v>
+        <v>-1.1526</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3174</v>
+        <v>-1.3163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1655</v>
+        <v>0.1637</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3655</v>
+        <v>-0.3644</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4754</v>
+        <v>-0.4742</v>
       </c>
       <c r="L7" t="n">
         <v>0.1098</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7864</v>
+        <v>-0.7883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8419</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05559999999999998</v>
+        <v>0.0539</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7013</v>
+        <v>0.7018</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7013</v>
+        <v>0.7018</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2473</v>
+        <v>0.2468</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01560000000000002</v>
+        <v>-0.0226</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2629</v>
+        <v>0.2693</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1351</v>
+        <v>0.1344</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8048</v>
+        <v>-1.8066</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5783</v>
+        <v>-1.5916</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2264</v>
+        <v>-0.2151</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7891</v>
+        <v>0.7843</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2555000000000001</v>
+        <v>-0.2576000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0445</v>
+        <v>1.0419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6804</v>
+        <v>0.6826</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9377000000000001</v>
+        <v>0.9374000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2572</v>
+        <v>-0.2548</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1087</v>
+        <v>0.1017</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1931</v>
+        <v>-1.1948</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3018</v>
+        <v>1.2967</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2338</v>
+        <v>0.2339</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4026</v>
+        <v>-1.4037</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6364</v>
+        <v>1.6375</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7627</v>
+        <v>-1.7607</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8561</v>
+        <v>-0.8703000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9064999999999999</v>
+        <v>-0.8903000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6834</v>
+        <v>-2.6821</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9925</v>
+        <v>-3.9943</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3092</v>
+        <v>1.3122</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9786</v>
+        <v>-0.9775</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2826</v>
+        <v>-0.2823</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.696</v>
+        <v>-0.6952</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5991</v>
+        <v>-1.5959</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7746</v>
+        <v>-0.7731</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8245</v>
+        <v>-0.8229</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6204</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.492</v>
+        <v>0.4908</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1284</v>
+        <v>0.1277</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8701</v>
+        <v>-1.8716</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3377</v>
+        <v>-2.3395</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1654</v>
+        <v>0.167</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0558</v>
+        <v>-0.0589</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2212</v>
+        <v>0.2259</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.842</v>
+        <v>-2.844600000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.385899999999999</v>
+        <v>-2.3992</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4560999999999999</v>
+        <v>-0.4453</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5691999999999999</v>
+        <v>-0.5713</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1012</v>
+        <v>-1.1004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5321</v>
+        <v>0.5291</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2357000000000001</v>
+        <v>-0.2339</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4187000000000001</v>
+        <v>-0.4168999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1831</v>
+        <v>0.183</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3335</v>
+        <v>-0.3373</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6823</v>
+        <v>-0.6835</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3489</v>
+        <v>0.346</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.8052</v>
+        <v>-2.8074</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7403</v>
+        <v>-3.7432</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9351</v>
+        <v>0.9357</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7947</v>
+        <v>0.7975</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2775</v>
+        <v>-0.2871</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0722</v>
+        <v>1.0845</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2623</v>
+        <v>-0.2633000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8676</v>
+        <v>1.8651</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1299</v>
+        <v>-2.1284</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2805</v>
+        <v>-3.2882</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1387</v>
+        <v>-3.1615</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1418999999999999</v>
+        <v>-0.1268</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5836</v>
+        <v>-2.5856</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8704</v>
+        <v>4.8616</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.4541</v>
+        <v>-7.4472</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7763000000000002</v>
+        <v>-0.7693</v>
       </c>
       <c r="K11" t="n">
-        <v>3.255</v>
+        <v>3.2528</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.0312</v>
+        <v>-4.0221</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8074</v>
+        <v>-1.8164</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6154</v>
+        <v>1.6087</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.4229</v>
+        <v>-3.4251</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7013</v>
+        <v>-0.7018</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.9091</v>
+        <v>-4.9129</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2077</v>
+        <v>4.211</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9426</v>
+        <v>-1.9454</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5438999999999998</v>
+        <v>0.5212</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.4867</v>
+        <v>-2.4666</v>
       </c>
       <c r="V11" t="n">
-        <v>1.947</v>
+        <v>1.9446</v>
       </c>
       <c r="W11" t="n">
-        <v>2.0026</v>
+        <v>1.9995</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0556</v>
+        <v>-0.0548</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.522600000000001</v>
+        <v>-6.5322</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3756</v>
+        <v>-6.4099</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.147</v>
+        <v>-0.1221999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6906</v>
+        <v>3.6856</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3616</v>
+        <v>3.355</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3289</v>
+        <v>0.3306</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4017</v>
+        <v>5.4097</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9328</v>
+        <v>2.9337</v>
       </c>
       <c r="L12" t="n">
-        <v>2.469</v>
+        <v>2.4761</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7111</v>
+        <v>-1.7242</v>
       </c>
       <c r="N12" t="n">
-        <v>0.429</v>
+        <v>0.4213000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1401</v>
+        <v>-2.1455</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.818200000000001</v>
+        <v>-9.825800000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.7921</v>
+        <v>-13.803</v>
       </c>
       <c r="R12" t="n">
-        <v>3.974</v>
+        <v>3.9771</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7446999999999999</v>
+        <v>-0.7402</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6798000000000001</v>
+        <v>0.6504000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4244</v>
+        <v>-1.3906</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3495999999999999</v>
+        <v>0.3483000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3351</v>
+        <v>1.333</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9855</v>
+        <v>-0.9847</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.0943</v>
+        <v>-10.0782</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.545500000000001</v>
+        <v>-9.5564</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5488</v>
+        <v>-0.5218000000000003</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.9375</v>
+        <v>-11.9174</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0733</v>
+        <v>-1.0731</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.8642</v>
+        <v>-10.8442</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.569599999999999</v>
+        <v>-9.537199999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.1713</v>
+        <v>-3.1623</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.398300000000001</v>
+        <v>-6.3749</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.368</v>
+        <v>-2.3802</v>
       </c>
       <c r="N13" t="n">
-        <v>2.098</v>
+        <v>2.0892</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.465999999999999</v>
+        <v>-4.4695</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1688</v>
+        <v>-1.1697</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.545500000000001</v>
+        <v>-6.550599999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>5.3767</v>
+        <v>5.3807</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9377</v>
+        <v>0.9353999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0397</v>
+        <v>2.0057</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1019</v>
+        <v>-1.0704</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0743</v>
+        <v>2.0735</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5298</v>
+        <v>4.5256</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4556</v>
+        <v>-2.4521</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.5291</v>
+        <v>-14.5381</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.3466</v>
+        <v>-19.5537</v>
       </c>
       <c r="F14" t="n">
-        <v>4.817700000000001</v>
+        <v>5.015500000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.891500000000001</v>
+        <v>-6.896899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>12.34</v>
+        <v>12.3132</v>
       </c>
       <c r="I14" t="n">
-        <v>-19.2316</v>
+        <v>-19.2102</v>
       </c>
       <c r="J14" t="n">
-        <v>1.106900000000001</v>
+        <v>1.203899999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3428</v>
+        <v>5.3733</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.235500000000001</v>
+        <v>-4.1691</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.9987</v>
+        <v>-8.1012</v>
       </c>
       <c r="N14" t="n">
-        <v>6.997999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.9964</v>
+        <v>-15.041</v>
       </c>
       <c r="P14" t="n">
-        <v>-15.1947</v>
+        <v>-15.2067</v>
       </c>
       <c r="Q14" t="n">
-        <v>-49.09100000000001</v>
+        <v>-49.1292</v>
       </c>
       <c r="R14" t="n">
-        <v>33.8961</v>
+        <v>33.9218</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8972000000000007</v>
+        <v>0.9116000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>7.704600000000001</v>
+        <v>7.4636</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.807199999999999</v>
+        <v>-6.552</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6598</v>
+        <v>6.6539</v>
       </c>
       <c r="W14" t="n">
-        <v>20.9326</v>
+        <v>20.9083</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.2729</v>
+        <v>-14.2542</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -565,67 +553,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3098</v>
+        <v>5.3085</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8876</v>
+        <v>5.8848</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5778999999999996</v>
+        <v>-0.5762999999999998</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6523</v>
+        <v>4.6508</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4449</v>
+        <v>6.443</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7927</v>
+        <v>-1.7922</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2613</v>
+        <v>5.2644</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6827</v>
+        <v>3.6837</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5786</v>
+        <v>1.5808</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.609</v>
+        <v>-0.6138000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7623</v>
+        <v>2.7592</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.3713</v>
+        <v>-3.373</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4036</v>
+        <v>-1.4037</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.9129</v>
+        <v>-4.9132</v>
       </c>
       <c r="R2" t="n">
-        <v>3.5092</v>
+        <v>3.5095</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7886000000000001</v>
+        <v>0.7887000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7504000000000001</v>
+        <v>0.7449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03820000000000001</v>
+        <v>0.04390000000000005</v>
       </c>
       <c r="V2" t="n">
         <v>1.2727</v>
       </c>
       <c r="W2" t="n">
-        <v>4.7889</v>
+        <v>4.788600000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.5162</v>
+        <v>-3.5158</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +631,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0825</v>
+        <v>5.0815</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8526</v>
+        <v>2.8496</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2299</v>
+        <v>2.2319</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2846</v>
+        <v>5.2832</v>
       </c>
       <c r="H3" t="n">
-        <v>5.431699999999999</v>
+        <v>5.4306</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1470999999999998</v>
+        <v>-0.1472999999999997</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3748</v>
+        <v>4.3787</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1698</v>
+        <v>4.1719</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2051000000000001</v>
+        <v>0.2070000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9097999999999999</v>
+        <v>0.9045</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2619</v>
+        <v>1.2587</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.352</v>
+        <v>-0.3542000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4036</v>
+        <v>1.4038</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0413</v>
+        <v>-3.0415</v>
       </c>
       <c r="R3" t="n">
-        <v>4.444900000000001</v>
+        <v>4.4453</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2538000000000001</v>
+        <v>0.2541</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1159</v>
+        <v>1.1094</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8621</v>
+        <v>-0.8552000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8596</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4032</v>
+        <v>0.403</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2628</v>
+        <v>-2.2626</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +709,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9594</v>
+        <v>2.9618</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1515</v>
+        <v>0.1518</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8079</v>
+        <v>2.8099</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.5213</v>
+        <v>-4.5196</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.5081</v>
+        <v>-2.5064</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0133</v>
+        <v>-2.0132</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.0932</v>
+        <v>-4.0857</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.0977</v>
+        <v>-4.0926</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004599999999999937</v>
+        <v>0.006699999999999928</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4283</v>
+        <v>-0.4339000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5896</v>
+        <v>1.5862</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0177</v>
+        <v>-2.02</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3395</v>
+        <v>2.3397</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8074</v>
+        <v>-2.8076</v>
       </c>
       <c r="R4" t="n">
-        <v>5.146800000000001</v>
+        <v>5.1473</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5967</v>
+        <v>1.5901</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3732</v>
+        <v>-1.3661</v>
       </c>
       <c r="V4" t="n">
         <v>4.9178</v>
       </c>
       <c r="W4" t="n">
-        <v>5.4554</v>
+        <v>5.4551</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5376</v>
+        <v>-0.5373</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +787,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6418999999999998</v>
+        <v>0.6407999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.08</v>
+        <v>-1.0836</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7219</v>
+        <v>1.7244</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5881000000000001</v>
+        <v>0.5868999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0761</v>
+        <v>-1.0765</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6642</v>
+        <v>1.6634</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0694</v>
+        <v>2.0734</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6788999999999998</v>
+        <v>-0.6765</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7484</v>
+        <v>2.7498</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4813</v>
+        <v>-1.4865</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3972000000000001</v>
+        <v>-0.4001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0842</v>
+        <v>-1.0864</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1056</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.6147</v>
+        <v>-5.615</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5092</v>
+        <v>3.5095</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9454</v>
+        <v>1.9457</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0622</v>
+        <v>2.0551</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1167</v>
+        <v>-0.1094</v>
       </c>
       <c r="V5" t="n">
         <v>0.2139</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4032</v>
+        <v>0.403</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1892</v>
+        <v>-0.1891</v>
       </c>
     </row>
     <row r="6">
@@ -877,19 +865,19 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -904,10 +892,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1661</v>
+        <v>-0.166</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -955,67 +943,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1337</v>
+        <v>-1.1344</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2524999999999999</v>
+        <v>-0.2535</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8812000000000001</v>
+        <v>-0.8808</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1526</v>
+        <v>-1.1532</v>
       </c>
       <c r="H7" t="n">
         <v>-1.3163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1637</v>
+        <v>0.163</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3644</v>
+        <v>-0.364</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4742</v>
+        <v>-0.4737999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>0.1098</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7883</v>
+        <v>-0.7892</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8425</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0539</v>
+        <v>0.05320000000000002</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7018</v>
+        <v>0.7019</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7018</v>
+        <v>0.7019</v>
       </c>
       <c r="S7" t="n">
         <v>0.2468</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0226</v>
+        <v>-0.02399999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2693</v>
+        <v>0.2707</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1344</v>
+        <v>0.1343</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1021,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8066</v>
+        <v>-1.8079</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5916</v>
+        <v>-1.5935</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2151</v>
+        <v>-0.2144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7843</v>
+        <v>0.7825000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2576000000000001</v>
+        <v>-0.2587</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0419</v>
+        <v>1.0412</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6826</v>
+        <v>0.6835</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9374000000000001</v>
+        <v>0.9376000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2548</v>
+        <v>-0.254</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1017</v>
+        <v>0.09889999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1948</v>
+        <v>-1.1963</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2967</v>
+        <v>1.2952</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4037</v>
+        <v>-1.4038</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6375</v>
+        <v>1.6378</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7607</v>
+        <v>-1.7601</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8703000000000001</v>
+        <v>-0.8732</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8903000000000001</v>
+        <v>-0.8868</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1099,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6821</v>
+        <v>-2.6817</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9943</v>
+        <v>-3.9942</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3122</v>
+        <v>1.3125</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9775</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>-0.2823</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6952</v>
+        <v>-0.695</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5959</v>
+        <v>-1.5951</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7731</v>
+        <v>-0.7726</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8229</v>
+        <v>-0.8225</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6178</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4908</v>
+        <v>0.4904</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1277</v>
+        <v>0.1274</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8716</v>
+        <v>-1.8717</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3395</v>
+        <v>-2.3396</v>
       </c>
       <c r="R9" t="n">
         <v>0.4679</v>
       </c>
       <c r="S9" t="n">
-        <v>0.167</v>
+        <v>0.1673</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0589</v>
+        <v>-0.0595</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2259</v>
+        <v>0.2268</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1177,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.844600000000001</v>
+        <v>-2.845299999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3992</v>
+        <v>-2.4009</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4453</v>
+        <v>-0.4444</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5713</v>
+        <v>-0.5721999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>-1.1004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5291</v>
+        <v>0.5283</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2339</v>
+        <v>-0.2333000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4168999999999999</v>
+        <v>-0.4163</v>
       </c>
       <c r="L10" t="n">
         <v>0.183</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3373</v>
+        <v>-0.339</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6835</v>
+        <v>-0.6842</v>
       </c>
       <c r="O10" t="n">
-        <v>0.346</v>
+        <v>0.3453</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.8074</v>
+        <v>-2.8075</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7432</v>
+        <v>-3.7434</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9357</v>
+        <v>0.9359</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7975</v>
+        <v>0.7978999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2871</v>
+        <v>-0.2891</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0845</v>
+        <v>1.087</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2633000000000001</v>
+        <v>-0.2634000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8651</v>
+        <v>1.8649</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1284</v>
+        <v>-2.1283</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1255,64 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2882</v>
+        <v>-3.2897</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1615</v>
+        <v>-3.1639</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1268</v>
+        <v>-0.1256999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5856</v>
+        <v>-2.5865</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8616</v>
+        <v>4.859400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.4472</v>
+        <v>-7.4459</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7693</v>
+        <v>-0.7665</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2528</v>
+        <v>3.2532</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.0221</v>
+        <v>-4.0195</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8164</v>
+        <v>-1.82</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6087</v>
+        <v>1.6063</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.4251</v>
+        <v>-3.4263</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7018</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.9129</v>
+        <v>-4.9132</v>
       </c>
       <c r="R11" t="n">
-        <v>4.211</v>
+        <v>4.2113</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9454</v>
+        <v>-1.9457</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5212</v>
+        <v>0.5165</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.4666</v>
+        <v>-2.4623</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9446</v>
+        <v>1.9445</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9995</v>
+        <v>1.9993</v>
       </c>
       <c r="X11" t="n">
         <v>-0.0548</v>
@@ -1345,67 +1333,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5322</v>
+        <v>-6.532999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4099</v>
+        <v>-6.4127</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1221999999999998</v>
+        <v>-0.1204</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6856</v>
+        <v>3.6845</v>
       </c>
       <c r="H12" t="n">
-        <v>3.355</v>
+        <v>3.3531</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3306</v>
+        <v>0.3311999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4097</v>
+        <v>5.414099999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9337</v>
+        <v>2.9355</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4761</v>
+        <v>2.4787</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7242</v>
+        <v>-1.7297</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4213000000000001</v>
+        <v>0.4177000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1455</v>
+        <v>-2.1474</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.825800000000001</v>
+        <v>-9.8264</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.803</v>
+        <v>-13.8038</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9771</v>
+        <v>3.9774</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7402</v>
+        <v>-0.7392000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6504000000000001</v>
+        <v>0.6443</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3906</v>
+        <v>-1.3835</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3483000000000001</v>
+        <v>0.3482999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>1.333</v>
+        <v>1.3329</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9847</v>
+        <v>-0.9846</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1411,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.0782</v>
+        <v>-10.0741</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.5564</v>
+        <v>-9.554600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5218000000000003</v>
+        <v>-0.5194999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.9174</v>
+        <v>-11.9127</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0731</v>
+        <v>-1.0734</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.8442</v>
+        <v>-10.8392</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.537199999999999</v>
+        <v>-9.5275</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.1623</v>
+        <v>-3.1593</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.3749</v>
+        <v>-6.3681</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3802</v>
+        <v>-2.3853</v>
       </c>
       <c r="N13" t="n">
-        <v>2.0892</v>
+        <v>2.0858</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.4695</v>
+        <v>-4.471</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1697</v>
+        <v>-1.1698</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.550599999999999</v>
+        <v>-6.551</v>
       </c>
       <c r="R13" t="n">
-        <v>5.3807</v>
+        <v>5.3811</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9353999999999999</v>
+        <v>0.9349000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0057</v>
+        <v>1.9984</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0704</v>
+        <v>-1.0636</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0735</v>
+        <v>2.0734</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5256</v>
+        <v>4.5252</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4521</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1489,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.5381</v>
+        <v>-14.5395</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.5537</v>
+        <v>-19.5707</v>
       </c>
       <c r="F14" t="n">
-        <v>5.015500000000001</v>
+        <v>5.0312</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.896899999999999</v>
+        <v>-6.8996</v>
       </c>
       <c r="H14" t="n">
-        <v>12.3132</v>
+        <v>12.3061</v>
       </c>
       <c r="I14" t="n">
-        <v>-19.2102</v>
+        <v>-19.2057</v>
       </c>
       <c r="J14" t="n">
-        <v>1.203899999999999</v>
+        <v>1.242000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3733</v>
+        <v>5.3908</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.1691</v>
+        <v>-4.1483</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.1012</v>
+        <v>-8.142199999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>6.94</v>
+        <v>6.9152</v>
       </c>
       <c r="O14" t="n">
-        <v>-15.041</v>
+        <v>-15.0572</v>
       </c>
       <c r="P14" t="n">
-        <v>-15.2067</v>
+        <v>-15.2073</v>
       </c>
       <c r="Q14" t="n">
-        <v>-49.1292</v>
+        <v>-49.1321</v>
       </c>
       <c r="R14" t="n">
-        <v>33.9218</v>
+        <v>33.92489999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9116000000000003</v>
+        <v>0.9144000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>7.4636</v>
+        <v>7.4129</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.552</v>
+        <v>-6.4985</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6539</v>
+        <v>6.653699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>20.9083</v>
+        <v>20.9063</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.2542</v>
+        <v>-14.2525</v>
       </c>
     </row>
   </sheetData>
